--- a/data/all_datasets/REDD/REDD_House6_stats/2026-03-23.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-03-23.xlsx
@@ -17256,7 +17256,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -17410,7 +17410,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E18" t="n">
